--- a/tabular/sublineage/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/sublineage/herv_sublineage_ltr_data_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0085EA3C-3721-2F43-903E-D16952DA913E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DD0AAF-8448-ED42-80BD-6D007F106EF4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="500" windowWidth="27480" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="500" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ltr_lineage_table" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="258">
   <si>
     <t>LTR_name</t>
   </si>
@@ -806,6 +806,27 @@
   </si>
   <si>
     <t>ERV-1.Rho.Rb.31</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda.57</t>
+  </si>
+  <si>
+    <t>LTR57</t>
+  </si>
+  <si>
+    <t>HERV-57</t>
+  </si>
+  <si>
+    <t>HARLEQUIN_LTR</t>
+  </si>
+  <si>
+    <t>HARLEQUIN</t>
+  </si>
+  <si>
+    <t>Eta</t>
+  </si>
+  <si>
+    <t>ERV-1.Eta.E.HQ</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1400,17 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1770,7 +1801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -1813,25 +1844,25 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>31</v>
+        <v>254</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>31</v>
+        <v>254</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>189</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>6</v>
+        <v>256</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>4</v>
@@ -1839,19 +1870,19 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>189</v>
@@ -1865,40 +1896,36 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>189</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="I4" t="str">
-        <f>IF(A4&lt;&gt;B4,"FLAG","")</f>
-        <v/>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>242</v>
+        <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>242</v>
+        <v>11</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>200</v>
@@ -1925,10 +1952,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>200</v>
@@ -1955,10 +1982,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>243</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>12</v>
+        <v>243</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>200</v>
@@ -1985,19 +2012,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>189</v>
@@ -2010,15 +2037,15 @@
       </c>
       <c r="I8" t="str">
         <f>IF(A8&lt;&gt;B8,"FLAG","")</f>
-        <v>FLAG</v>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>236</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>200</v>
@@ -2038,22 +2065,26 @@
       <c r="H9" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="I9" t="str">
+        <f>IF(A9&lt;&gt;B9,"FLAG","")</f>
+        <v>FLAG</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>16</v>
+        <v>235</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>189</v>
@@ -2064,17 +2095,13 @@
       <c r="H10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I10" t="str">
-        <f>IF(A10&lt;&gt;B10,"FLAG","")</f>
-        <v/>
-      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>200</v>
@@ -2095,25 +2122,25 @@
         <v>4</v>
       </c>
       <c r="I11" t="str">
-        <f>IF(A11&lt;&gt;B11,"FLAG","")</f>
+        <f t="shared" ref="I11:I42" si="0">IF(A11&lt;&gt;B11,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>189</v>
@@ -2125,16 +2152,16 @@
         <v>4</v>
       </c>
       <c r="I12" t="str">
-        <f>IF(A12&lt;&gt;B12,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>200</v>
@@ -2155,25 +2182,25 @@
         <v>4</v>
       </c>
       <c r="I13" t="str">
-        <f>IF(A13&lt;&gt;B13,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>189</v>
@@ -2185,25 +2212,25 @@
         <v>4</v>
       </c>
       <c r="I14" t="str">
-        <f>IF(A14&lt;&gt;B14,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>189</v>
@@ -2215,16 +2242,16 @@
         <v>4</v>
       </c>
       <c r="I15" t="str">
-        <f>IF(A15&lt;&gt;B15,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>200</v>
@@ -2245,16 +2272,16 @@
         <v>4</v>
       </c>
       <c r="I16" t="str">
-        <f>IF(A16&lt;&gt;B16,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>200</v>
@@ -2275,25 +2302,25 @@
         <v>4</v>
       </c>
       <c r="I17" t="str">
-        <f>IF(A17&lt;&gt;B17,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>189</v>
@@ -2305,16 +2332,16 @@
         <v>4</v>
       </c>
       <c r="I18" t="str">
-        <f>IF(A18&lt;&gt;B18,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>200</v>
@@ -2335,16 +2362,16 @@
         <v>4</v>
       </c>
       <c r="I19" t="str">
-        <f>IF(A19&lt;&gt;B19,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>200</v>
@@ -2365,16 +2392,16 @@
         <v>4</v>
       </c>
       <c r="I20" t="str">
-        <f>IF(A20&lt;&gt;B20,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>200</v>
@@ -2395,25 +2422,25 @@
         <v>4</v>
       </c>
       <c r="I21" t="str">
-        <f>IF(A21&lt;&gt;B21,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>189</v>
@@ -2425,25 +2452,25 @@
         <v>4</v>
       </c>
       <c r="I22" t="str">
-        <f>IF(A22&lt;&gt;B22,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>189</v>
@@ -2455,16 +2482,16 @@
         <v>4</v>
       </c>
       <c r="I23" t="str">
-        <f>IF(A23&lt;&gt;B23,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>200</v>
@@ -2485,16 +2512,16 @@
         <v>4</v>
       </c>
       <c r="I24" t="str">
-        <f>IF(A24&lt;&gt;B24,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>200</v>
@@ -2515,16 +2542,16 @@
         <v>4</v>
       </c>
       <c r="I25" t="str">
-        <f>IF(A25&lt;&gt;B25,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>200</v>
@@ -2545,16 +2572,16 @@
         <v>4</v>
       </c>
       <c r="I26" t="str">
-        <f>IF(A26&lt;&gt;B26,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>200</v>
@@ -2575,16 +2602,16 @@
         <v>4</v>
       </c>
       <c r="I27" t="str">
-        <f>IF(A27&lt;&gt;B27,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>200</v>
@@ -2605,16 +2632,16 @@
         <v>4</v>
       </c>
       <c r="I28" t="str">
-        <f>IF(A28&lt;&gt;B28,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>200</v>
@@ -2635,16 +2662,16 @@
         <v>4</v>
       </c>
       <c r="I29" t="str">
-        <f>IF(A29&lt;&gt;B29,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>200</v>
@@ -2665,25 +2692,25 @@
         <v>4</v>
       </c>
       <c r="I30" t="str">
-        <f>IF(A30&lt;&gt;B30,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>189</v>
@@ -2695,16 +2722,16 @@
         <v>4</v>
       </c>
       <c r="I31" t="str">
-        <f>IF(A31&lt;&gt;B31,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>244</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>44</v>
+        <v>244</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>200</v>
@@ -2725,25 +2752,25 @@
         <v>4</v>
       </c>
       <c r="I32" t="str">
-        <f>IF(A32&lt;&gt;B32,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>189</v>
@@ -2755,25 +2782,25 @@
         <v>4</v>
       </c>
       <c r="I33" t="str">
-        <f>IF(A33&lt;&gt;B33,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>189</v>
@@ -2785,16 +2812,16 @@
         <v>4</v>
       </c>
       <c r="I34" t="str">
-        <f>IF(A34&lt;&gt;B34,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>200</v>
@@ -2815,16 +2842,16 @@
         <v>4</v>
       </c>
       <c r="I35" t="str">
-        <f>IF(A35&lt;&gt;B35,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>200</v>
@@ -2845,16 +2872,16 @@
         <v>4</v>
       </c>
       <c r="I36" t="str">
-        <f>IF(A36&lt;&gt;B36,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>200</v>
@@ -2875,25 +2902,25 @@
         <v>4</v>
       </c>
       <c r="I37" t="str">
-        <f>IF(A37&lt;&gt;B37,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>189</v>
@@ -2905,38 +2932,38 @@
         <v>4</v>
       </c>
       <c r="I38" t="str">
-        <f>IF(A38&lt;&gt;B38,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>189</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="I39" t="str">
-        <f>IF(A39&lt;&gt;B39,"FLAG","")</f>
-        <v>FLAG</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
@@ -2944,7 +2971,7 @@
         <v>61</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>200</v>
@@ -2965,16 +2992,16 @@
         <v>56</v>
       </c>
       <c r="I40" t="str">
-        <f>IF(A40&lt;&gt;B40,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v>FLAG</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>200</v>
@@ -2995,16 +3022,16 @@
         <v>56</v>
       </c>
       <c r="I41" t="str">
-        <f>IF(A41&lt;&gt;B41,"FLAG","")</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>FLAG</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>200</v>
@@ -3025,16 +3052,16 @@
         <v>56</v>
       </c>
       <c r="I42" t="str">
-        <f>IF(A42&lt;&gt;B42,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>200</v>
@@ -3055,16 +3082,16 @@
         <v>56</v>
       </c>
       <c r="I43" t="str">
-        <f>IF(A43&lt;&gt;B43,"FLAG","")</f>
+        <f t="shared" ref="I43:I74" si="1">IF(A43&lt;&gt;B43,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>200</v>
@@ -3085,57 +3112,57 @@
         <v>56</v>
       </c>
       <c r="I44" t="str">
-        <f>IF(A44&lt;&gt;B44,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" s="6" t="s">
         <v>189</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>55</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="I45" t="str">
-        <f>IF(A45&lt;&gt;B45,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F46" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>189</v>
       </c>
       <c r="G46" s="5" t="s">
@@ -3145,16 +3172,16 @@
         <v>4</v>
       </c>
       <c r="I46" t="str">
-        <f>IF(A46&lt;&gt;B46,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>200</v>
@@ -3175,25 +3202,25 @@
         <v>4</v>
       </c>
       <c r="I47" t="str">
-        <f>IF(A47&lt;&gt;B47,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>189</v>
@@ -3205,16 +3232,16 @@
         <v>4</v>
       </c>
       <c r="I48" t="str">
-        <f>IF(A48&lt;&gt;B48,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>200</v>
@@ -3235,16 +3262,16 @@
         <v>4</v>
       </c>
       <c r="I49" t="str">
-        <f>IF(A49&lt;&gt;B49,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>200</v>
@@ -3265,16 +3292,16 @@
         <v>4</v>
       </c>
       <c r="I50" t="str">
-        <f>IF(A50&lt;&gt;B50,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>200</v>
@@ -3295,16 +3322,16 @@
         <v>4</v>
       </c>
       <c r="I51" t="str">
-        <f>IF(A51&lt;&gt;B51,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>200</v>
@@ -3325,16 +3352,16 @@
         <v>4</v>
       </c>
       <c r="I52" t="str">
-        <f>IF(A52&lt;&gt;B52,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>200</v>
@@ -3355,25 +3382,25 @@
         <v>4</v>
       </c>
       <c r="I53" t="str">
-        <f>IF(A53&lt;&gt;B53,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>189</v>
@@ -3385,16 +3412,16 @@
         <v>4</v>
       </c>
       <c r="I54" t="str">
-        <f>IF(A54&lt;&gt;B54,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>200</v>
@@ -3415,16 +3442,16 @@
         <v>4</v>
       </c>
       <c r="I55" t="str">
-        <f>IF(A55&lt;&gt;B55,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>200</v>
@@ -3445,16 +3472,16 @@
         <v>4</v>
       </c>
       <c r="I56" t="str">
-        <f>IF(A56&lt;&gt;B56,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>200</v>
@@ -3475,16 +3502,16 @@
         <v>4</v>
       </c>
       <c r="I57" t="str">
-        <f>IF(A57&lt;&gt;B57,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>200</v>
@@ -3505,16 +3532,16 @@
         <v>4</v>
       </c>
       <c r="I58" t="str">
-        <f>IF(A58&lt;&gt;B58,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>200</v>
@@ -3535,16 +3562,16 @@
         <v>4</v>
       </c>
       <c r="I59" t="str">
-        <f>IF(A59&lt;&gt;B59,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>200</v>
@@ -3565,16 +3592,16 @@
         <v>4</v>
       </c>
       <c r="I60" t="str">
-        <f>IF(A60&lt;&gt;B60,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>200</v>
@@ -3595,16 +3622,16 @@
         <v>4</v>
       </c>
       <c r="I61" t="str">
-        <f>IF(A61&lt;&gt;B61,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>200</v>
@@ -3625,16 +3652,16 @@
         <v>4</v>
       </c>
       <c r="I62" t="str">
-        <f>IF(A62&lt;&gt;B62,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>200</v>
@@ -3655,16 +3682,16 @@
         <v>4</v>
       </c>
       <c r="I63" t="str">
-        <f>IF(A63&lt;&gt;B63,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>200</v>
@@ -3685,16 +3712,16 @@
         <v>4</v>
       </c>
       <c r="I64" t="str">
-        <f>IF(A64&lt;&gt;B64,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>200</v>
@@ -3715,16 +3742,16 @@
         <v>4</v>
       </c>
       <c r="I65" t="str">
-        <f>IF(A65&lt;&gt;B65,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>200</v>
@@ -3745,16 +3772,16 @@
         <v>4</v>
       </c>
       <c r="I66" t="str">
-        <f>IF(A66&lt;&gt;B66,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>200</v>
@@ -3775,16 +3802,16 @@
         <v>4</v>
       </c>
       <c r="I67" t="str">
-        <f>IF(A67&lt;&gt;B67,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>200</v>
@@ -3805,16 +3832,16 @@
         <v>4</v>
       </c>
       <c r="I68" t="str">
-        <f>IF(A68&lt;&gt;B68,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>200</v>
@@ -3835,25 +3862,25 @@
         <v>4</v>
       </c>
       <c r="I69" t="str">
-        <f>IF(A69&lt;&gt;B69,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>189</v>
@@ -3865,16 +3892,16 @@
         <v>4</v>
       </c>
       <c r="I70" t="str">
-        <f>IF(A70&lt;&gt;B70,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>200</v>
@@ -3895,16 +3922,16 @@
         <v>4</v>
       </c>
       <c r="I71" t="str">
-        <f>IF(A71&lt;&gt;B71,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>200</v>
@@ -3925,16 +3952,16 @@
         <v>4</v>
       </c>
       <c r="I72" t="str">
-        <f>IF(A72&lt;&gt;B72,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>200</v>
@@ -3955,16 +3982,16 @@
         <v>4</v>
       </c>
       <c r="I73" t="str">
-        <f>IF(A73&lt;&gt;B73,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>200</v>
@@ -3985,25 +4012,25 @@
         <v>4</v>
       </c>
       <c r="I74" t="str">
-        <f>IF(A74&lt;&gt;B74,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>189</v>
@@ -4015,16 +4042,16 @@
         <v>4</v>
       </c>
       <c r="I75" t="str">
-        <f>IF(A75&lt;&gt;B75,"FLAG","")</f>
+        <f t="shared" ref="I75:I91" si="2">IF(A75&lt;&gt;B75,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>200</v>
@@ -4045,16 +4072,16 @@
         <v>4</v>
       </c>
       <c r="I76" t="str">
-        <f>IF(A76&lt;&gt;B76,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>200</v>
@@ -4075,16 +4102,16 @@
         <v>4</v>
       </c>
       <c r="I77" t="str">
-        <f>IF(A77&lt;&gt;B77,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>200</v>
@@ -4105,16 +4132,16 @@
         <v>4</v>
       </c>
       <c r="I78" t="str">
-        <f>IF(A78&lt;&gt;B78,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>200</v>
@@ -4135,16 +4162,16 @@
         <v>4</v>
       </c>
       <c r="I79" t="str">
-        <f>IF(A79&lt;&gt;B79,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>200</v>
@@ -4165,16 +4192,16 @@
         <v>4</v>
       </c>
       <c r="I80" t="str">
-        <f>IF(A80&lt;&gt;B80,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>200</v>
@@ -4195,16 +4222,16 @@
         <v>4</v>
       </c>
       <c r="I81" t="str">
-        <f>IF(A81&lt;&gt;B81,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>200</v>
@@ -4225,16 +4252,16 @@
         <v>4</v>
       </c>
       <c r="I82" t="str">
-        <f>IF(A82&lt;&gt;B82,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>200</v>
@@ -4255,16 +4282,16 @@
         <v>4</v>
       </c>
       <c r="I83" t="str">
-        <f>IF(A83&lt;&gt;B83,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>200</v>
@@ -4285,16 +4312,16 @@
         <v>4</v>
       </c>
       <c r="I84" t="str">
-        <f>IF(A84&lt;&gt;B84,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>200</v>
@@ -4315,16 +4342,16 @@
         <v>4</v>
       </c>
       <c r="I85" t="str">
-        <f>IF(A85&lt;&gt;B85,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>200</v>
@@ -4345,25 +4372,25 @@
         <v>4</v>
       </c>
       <c r="I86" t="str">
-        <f>IF(A86&lt;&gt;B86,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>189</v>
@@ -4375,25 +4402,25 @@
         <v>4</v>
       </c>
       <c r="I87" t="str">
-        <f>IF(A87&lt;&gt;B87,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>189</v>
@@ -4405,16 +4432,16 @@
         <v>4</v>
       </c>
       <c r="I88" t="str">
-        <f>IF(A88&lt;&gt;B88,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>200</v>
@@ -4435,25 +4462,25 @@
         <v>4</v>
       </c>
       <c r="I89" t="str">
-        <f>IF(A89&lt;&gt;B89,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>189</v>
@@ -4465,25 +4492,25 @@
         <v>4</v>
       </c>
       <c r="I90" t="str">
-        <f>IF(A90&lt;&gt;B90,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>239</v>
+        <v>119</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>239</v>
+        <v>119</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>238</v>
+        <v>120</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>189</v>
@@ -4494,22 +4521,26 @@
       <c r="H91" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="I91" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>61</v>
+        <v>239</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>61</v>
+        <v>239</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>200</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>58</v>
+        <v>238</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>189</v>
@@ -4523,10 +4554,10 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>248</v>
+        <v>61</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>248</v>
+        <v>61</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>200</v>
@@ -4549,10 +4580,10 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>62</v>
+        <v>248</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>62</v>
+        <v>248</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>200</v>
@@ -4575,10 +4606,10 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>200</v>
@@ -4601,10 +4632,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>200</v>
@@ -4627,10 +4658,10 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>200</v>
@@ -4653,49 +4684,45 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>189</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="I98" t="str">
-        <f>IF(A98&lt;&gt;B98,"FLAG","")</f>
-        <v/>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>189</v>
@@ -4707,25 +4734,25 @@
         <v>4</v>
       </c>
       <c r="I99" t="str">
-        <f>IF(A99&lt;&gt;B99,"FLAG","")</f>
+        <f t="shared" ref="I99:I128" si="3">IF(A99&lt;&gt;B99,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>189</v>
@@ -4737,25 +4764,25 @@
         <v>4</v>
       </c>
       <c r="I100" t="str">
-        <f>IF(A100&lt;&gt;B100,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>189</v>
@@ -4767,16 +4794,16 @@
         <v>4</v>
       </c>
       <c r="I101" t="str">
-        <f>IF(A101&lt;&gt;B101,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>201</v>
@@ -4797,16 +4824,16 @@
         <v>4</v>
       </c>
       <c r="I102" t="str">
-        <f>IF(A102&lt;&gt;B102,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>201</v>
@@ -4827,16 +4854,16 @@
         <v>4</v>
       </c>
       <c r="I103" t="str">
-        <f>IF(A103&lt;&gt;B103,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>201</v>
@@ -4857,16 +4884,16 @@
         <v>4</v>
       </c>
       <c r="I104" t="str">
-        <f>IF(A104&lt;&gt;B104,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>201</v>
@@ -4887,16 +4914,16 @@
         <v>4</v>
       </c>
       <c r="I105" t="str">
-        <f>IF(A105&lt;&gt;B105,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>201</v>
@@ -4917,16 +4944,16 @@
         <v>4</v>
       </c>
       <c r="I106" t="str">
-        <f>IF(A106&lt;&gt;B106,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>201</v>
@@ -4947,16 +4974,16 @@
         <v>4</v>
       </c>
       <c r="I107" t="str">
-        <f>IF(A107&lt;&gt;B107,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>201</v>
@@ -4977,16 +5004,16 @@
         <v>4</v>
       </c>
       <c r="I108" t="str">
-        <f>IF(A108&lt;&gt;B108,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>201</v>
@@ -5007,16 +5034,16 @@
         <v>4</v>
       </c>
       <c r="I109" t="str">
-        <f>IF(A109&lt;&gt;B109,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>201</v>
@@ -5037,16 +5064,16 @@
         <v>4</v>
       </c>
       <c r="I110" t="str">
-        <f>IF(A110&lt;&gt;B110,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>201</v>
@@ -5067,16 +5094,16 @@
         <v>4</v>
       </c>
       <c r="I111" t="str">
-        <f>IF(A111&lt;&gt;B111,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>201</v>
@@ -5097,16 +5124,16 @@
         <v>4</v>
       </c>
       <c r="I112" t="str">
-        <f>IF(A112&lt;&gt;B112,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>201</v>
@@ -5127,25 +5154,25 @@
         <v>4</v>
       </c>
       <c r="I113" t="str">
-        <f>IF(A113&lt;&gt;B113,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>189</v>
@@ -5157,25 +5184,25 @@
         <v>4</v>
       </c>
       <c r="I114" t="str">
-        <f>IF(A114&lt;&gt;B114,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>189</v>
@@ -5187,25 +5214,25 @@
         <v>4</v>
       </c>
       <c r="I115" t="str">
-        <f>IF(A115&lt;&gt;B115,"FLAG","")</f>
-        <v>FLAG</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>189</v>
@@ -5217,16 +5244,16 @@
         <v>4</v>
       </c>
       <c r="I116" t="str">
-        <f>IF(A116&lt;&gt;B116,"FLAG","")</f>
-        <v/>
+        <f t="shared" si="3"/>
+        <v>FLAG</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>201</v>
@@ -5247,16 +5274,16 @@
         <v>4</v>
       </c>
       <c r="I117" t="str">
-        <f>IF(A117&lt;&gt;B117,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>201</v>
@@ -5277,16 +5304,16 @@
         <v>4</v>
       </c>
       <c r="I118" t="str">
-        <f>IF(A118&lt;&gt;B118,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>201</v>
@@ -5307,25 +5334,25 @@
         <v>4</v>
       </c>
       <c r="I119" t="str">
-        <f>IF(A119&lt;&gt;B119,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>189</v>
@@ -5337,16 +5364,16 @@
         <v>4</v>
       </c>
       <c r="I120" t="str">
-        <f>IF(A120&lt;&gt;B120,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>201</v>
@@ -5367,16 +5394,16 @@
         <v>4</v>
       </c>
       <c r="I121" t="str">
-        <f>IF(A121&lt;&gt;B121,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>201</v>
@@ -5397,25 +5424,25 @@
         <v>4</v>
       </c>
       <c r="I122" t="str">
-        <f>IF(A122&lt;&gt;B122,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>189</v>
@@ -5427,25 +5454,25 @@
         <v>4</v>
       </c>
       <c r="I123" t="str">
-        <f>IF(A123&lt;&gt;B123,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>189</v>
@@ -5457,16 +5484,16 @@
         <v>4</v>
       </c>
       <c r="I124" t="str">
-        <f>IF(A124&lt;&gt;B124,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>201</v>
@@ -5487,16 +5514,16 @@
         <v>4</v>
       </c>
       <c r="I125" t="str">
-        <f>IF(A125&lt;&gt;B125,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>201</v>
@@ -5517,25 +5544,25 @@
         <v>4</v>
       </c>
       <c r="I126" t="str">
-        <f>IF(A126&lt;&gt;B126,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>189</v>
@@ -5547,25 +5574,25 @@
         <v>4</v>
       </c>
       <c r="I127" t="str">
-        <f>IF(A127&lt;&gt;B127,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>189</v>
@@ -5576,22 +5603,26 @@
       <c r="H128" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="I128" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>161</v>
+        <v>245</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>161</v>
+        <v>245</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>189</v>
@@ -5605,10 +5636,10 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>201</v>
@@ -5629,18 +5660,70 @@
         <v>4</v>
       </c>
     </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A131" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A132" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I130">
-    <sortCondition ref="C2:C130"/>
-    <sortCondition ref="G2:G130"/>
-    <sortCondition ref="H2:H130"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I131">
+    <sortCondition ref="C3:C131"/>
+    <sortCondition ref="G3:G131"/>
+    <sortCondition ref="H3:H131"/>
   </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="I115:I116">
-    <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I115)))</formula>
+  <conditionalFormatting sqref="I116:I117">
+    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I116)))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5651,11 +5734,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I31:I114 I2:I3 I6:I29">
-    <cfRule type="containsText" dxfId="6" priority="41" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
+  <conditionalFormatting sqref="I32:I115 I3:I4 I7:I30">
+    <cfRule type="containsText" dxfId="7" priority="43" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I3)))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5666,9 +5749,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
+  <conditionalFormatting sqref="I5">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I5)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I4)))</formula>
+      <formula>NOT(ISERROR(SEARCH("FLAG",I6)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -5681,9 +5779,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5">
+  <conditionalFormatting sqref="I31">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I5)))</formula>
+      <formula>NOT(ISERROR(SEARCH("FLAG",I31)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -5696,9 +5794,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I30">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I30)))</formula>
+  <conditionalFormatting sqref="I2">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -6463,7 +6561,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I22">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -6478,7 +6576,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -6493,7 +6591,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:I25">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I24)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">

--- a/tabular/sublineage/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/sublineage/herv_sublineage_ltr_data_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DD0AAF-8448-ED42-80BD-6D007F106EF4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C708C70E-DD6C-F54B-91D1-ECF75CC54BC4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="500" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="720" windowWidth="21060" windowHeight="16940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ltr_lineage_table" sheetId="1" r:id="rId1"/>
@@ -1400,7 +1400,17 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1801,7 +1811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -2122,7 +2132,7 @@
         <v>4</v>
       </c>
       <c r="I11" t="str">
-        <f t="shared" ref="I11:I42" si="0">IF(A11&lt;&gt;B11,"FLAG","")</f>
+        <f>IF(A11&lt;&gt;B11,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2152,7 +2162,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A12&lt;&gt;B12,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2182,7 +2192,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A13&lt;&gt;B13,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2212,7 +2222,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A14&lt;&gt;B14,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2242,7 +2252,7 @@
         <v>4</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A15&lt;&gt;B15,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2272,7 +2282,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A16&lt;&gt;B16,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2302,7 +2312,7 @@
         <v>4</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A17&lt;&gt;B17,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2332,7 +2342,7 @@
         <v>4</v>
       </c>
       <c r="I18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A18&lt;&gt;B18,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2362,7 +2372,7 @@
         <v>4</v>
       </c>
       <c r="I19" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A19&lt;&gt;B19,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2392,7 +2402,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A20&lt;&gt;B20,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2422,7 +2432,7 @@
         <v>4</v>
       </c>
       <c r="I21" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A21&lt;&gt;B21,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2452,7 +2462,7 @@
         <v>4</v>
       </c>
       <c r="I22" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A22&lt;&gt;B22,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2482,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A23&lt;&gt;B23,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2512,7 +2522,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A24&lt;&gt;B24,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2542,7 +2552,7 @@
         <v>4</v>
       </c>
       <c r="I25" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A25&lt;&gt;B25,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2572,7 +2582,7 @@
         <v>4</v>
       </c>
       <c r="I26" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A26&lt;&gt;B26,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2602,7 +2612,7 @@
         <v>4</v>
       </c>
       <c r="I27" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A27&lt;&gt;B27,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2632,7 +2642,7 @@
         <v>4</v>
       </c>
       <c r="I28" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A28&lt;&gt;B28,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2662,7 +2672,7 @@
         <v>4</v>
       </c>
       <c r="I29" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A29&lt;&gt;B29,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2692,7 +2702,7 @@
         <v>4</v>
       </c>
       <c r="I30" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A30&lt;&gt;B30,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2722,7 +2732,7 @@
         <v>4</v>
       </c>
       <c r="I31" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A31&lt;&gt;B31,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2752,7 +2762,7 @@
         <v>4</v>
       </c>
       <c r="I32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A32&lt;&gt;B32,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2782,7 +2792,7 @@
         <v>4</v>
       </c>
       <c r="I33" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A33&lt;&gt;B33,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2812,7 +2822,7 @@
         <v>4</v>
       </c>
       <c r="I34" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A34&lt;&gt;B34,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2842,7 +2852,7 @@
         <v>4</v>
       </c>
       <c r="I35" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A35&lt;&gt;B35,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2872,7 +2882,7 @@
         <v>4</v>
       </c>
       <c r="I36" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A36&lt;&gt;B36,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2902,7 +2912,7 @@
         <v>4</v>
       </c>
       <c r="I37" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A37&lt;&gt;B37,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2932,7 +2942,7 @@
         <v>4</v>
       </c>
       <c r="I38" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A38&lt;&gt;B38,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2962,7 +2972,7 @@
         <v>4</v>
       </c>
       <c r="I39" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A39&lt;&gt;B39,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2992,7 +3002,7 @@
         <v>56</v>
       </c>
       <c r="I40" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A40&lt;&gt;B40,"FLAG","")</f>
         <v>FLAG</v>
       </c>
     </row>
@@ -3022,7 +3032,7 @@
         <v>56</v>
       </c>
       <c r="I41" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A41&lt;&gt;B41,"FLAG","")</f>
         <v>FLAG</v>
       </c>
     </row>
@@ -3052,7 +3062,7 @@
         <v>56</v>
       </c>
       <c r="I42" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A42&lt;&gt;B42,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3082,7 +3092,7 @@
         <v>56</v>
       </c>
       <c r="I43" t="str">
-        <f t="shared" ref="I43:I74" si="1">IF(A43&lt;&gt;B43,"FLAG","")</f>
+        <f>IF(A43&lt;&gt;B43,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3112,7 +3122,7 @@
         <v>56</v>
       </c>
       <c r="I44" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A44&lt;&gt;B44,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3142,7 +3152,7 @@
         <v>56</v>
       </c>
       <c r="I45" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A45&lt;&gt;B45,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3172,7 +3182,7 @@
         <v>4</v>
       </c>
       <c r="I46" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A46&lt;&gt;B46,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3202,7 +3212,7 @@
         <v>4</v>
       </c>
       <c r="I47" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A47&lt;&gt;B47,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3232,7 +3242,7 @@
         <v>4</v>
       </c>
       <c r="I48" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A48&lt;&gt;B48,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3262,7 +3272,7 @@
         <v>4</v>
       </c>
       <c r="I49" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A49&lt;&gt;B49,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3292,7 +3302,7 @@
         <v>4</v>
       </c>
       <c r="I50" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A50&lt;&gt;B50,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3322,7 +3332,7 @@
         <v>4</v>
       </c>
       <c r="I51" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A51&lt;&gt;B51,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3352,7 +3362,7 @@
         <v>4</v>
       </c>
       <c r="I52" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A52&lt;&gt;B52,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3382,7 +3392,7 @@
         <v>4</v>
       </c>
       <c r="I53" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A53&lt;&gt;B53,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3412,7 +3422,7 @@
         <v>4</v>
       </c>
       <c r="I54" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A54&lt;&gt;B54,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3442,7 +3452,7 @@
         <v>4</v>
       </c>
       <c r="I55" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A55&lt;&gt;B55,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3472,7 +3482,7 @@
         <v>4</v>
       </c>
       <c r="I56" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A56&lt;&gt;B56,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3502,7 +3512,7 @@
         <v>4</v>
       </c>
       <c r="I57" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A57&lt;&gt;B57,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3532,7 +3542,7 @@
         <v>4</v>
       </c>
       <c r="I58" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A58&lt;&gt;B58,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3562,7 +3572,7 @@
         <v>4</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A59&lt;&gt;B59,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3592,7 +3602,7 @@
         <v>4</v>
       </c>
       <c r="I60" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A60&lt;&gt;B60,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3622,7 +3632,7 @@
         <v>4</v>
       </c>
       <c r="I61" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A61&lt;&gt;B61,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3652,7 +3662,7 @@
         <v>4</v>
       </c>
       <c r="I62" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A62&lt;&gt;B62,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3682,7 +3692,7 @@
         <v>4</v>
       </c>
       <c r="I63" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A63&lt;&gt;B63,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3712,7 +3722,7 @@
         <v>4</v>
       </c>
       <c r="I64" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A64&lt;&gt;B64,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3742,7 +3752,7 @@
         <v>4</v>
       </c>
       <c r="I65" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A65&lt;&gt;B65,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3772,7 +3782,7 @@
         <v>4</v>
       </c>
       <c r="I66" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A66&lt;&gt;B66,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3802,7 +3812,7 @@
         <v>4</v>
       </c>
       <c r="I67" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A67&lt;&gt;B67,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3832,7 +3842,7 @@
         <v>4</v>
       </c>
       <c r="I68" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A68&lt;&gt;B68,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3862,7 +3872,7 @@
         <v>4</v>
       </c>
       <c r="I69" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A69&lt;&gt;B69,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3892,7 +3902,7 @@
         <v>4</v>
       </c>
       <c r="I70" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A70&lt;&gt;B70,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3922,7 +3932,7 @@
         <v>4</v>
       </c>
       <c r="I71" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A71&lt;&gt;B71,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3952,7 +3962,7 @@
         <v>4</v>
       </c>
       <c r="I72" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A72&lt;&gt;B72,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3992,7 @@
         <v>4</v>
       </c>
       <c r="I73" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A73&lt;&gt;B73,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4012,7 +4022,7 @@
         <v>4</v>
       </c>
       <c r="I74" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A74&lt;&gt;B74,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4042,7 +4052,7 @@
         <v>4</v>
       </c>
       <c r="I75" t="str">
-        <f t="shared" ref="I75:I91" si="2">IF(A75&lt;&gt;B75,"FLAG","")</f>
+        <f>IF(A75&lt;&gt;B75,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4072,7 +4082,7 @@
         <v>4</v>
       </c>
       <c r="I76" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A76&lt;&gt;B76,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4102,7 +4112,7 @@
         <v>4</v>
       </c>
       <c r="I77" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A77&lt;&gt;B77,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4132,7 +4142,7 @@
         <v>4</v>
       </c>
       <c r="I78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A78&lt;&gt;B78,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4162,7 +4172,7 @@
         <v>4</v>
       </c>
       <c r="I79" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A79&lt;&gt;B79,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4192,7 +4202,7 @@
         <v>4</v>
       </c>
       <c r="I80" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A80&lt;&gt;B80,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4222,7 +4232,7 @@
         <v>4</v>
       </c>
       <c r="I81" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A81&lt;&gt;B81,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4252,7 +4262,7 @@
         <v>4</v>
       </c>
       <c r="I82" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A82&lt;&gt;B82,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4282,7 +4292,7 @@
         <v>4</v>
       </c>
       <c r="I83" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A83&lt;&gt;B83,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4312,7 +4322,7 @@
         <v>4</v>
       </c>
       <c r="I84" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A84&lt;&gt;B84,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4342,7 +4352,7 @@
         <v>4</v>
       </c>
       <c r="I85" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A85&lt;&gt;B85,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4372,7 +4382,7 @@
         <v>4</v>
       </c>
       <c r="I86" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A86&lt;&gt;B86,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4402,7 +4412,7 @@
         <v>4</v>
       </c>
       <c r="I87" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A87&lt;&gt;B87,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4432,7 +4442,7 @@
         <v>4</v>
       </c>
       <c r="I88" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A88&lt;&gt;B88,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4462,7 +4472,7 @@
         <v>4</v>
       </c>
       <c r="I89" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A89&lt;&gt;B89,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4492,7 +4502,7 @@
         <v>4</v>
       </c>
       <c r="I90" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A90&lt;&gt;B90,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4522,7 +4532,7 @@
         <v>4</v>
       </c>
       <c r="I91" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A91&lt;&gt;B91,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4710,19 +4720,19 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>189</v>
@@ -4734,25 +4744,25 @@
         <v>4</v>
       </c>
       <c r="I99" t="str">
-        <f t="shared" ref="I99:I128" si="3">IF(A99&lt;&gt;B99,"FLAG","")</f>
+        <f>IF(A99&lt;&gt;B99,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>189</v>
@@ -4764,25 +4774,25 @@
         <v>4</v>
       </c>
       <c r="I100" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A100&lt;&gt;B100,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>189</v>
@@ -4794,16 +4804,16 @@
         <v>4</v>
       </c>
       <c r="I101" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A101&lt;&gt;B101,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>201</v>
@@ -4824,16 +4834,16 @@
         <v>4</v>
       </c>
       <c r="I102" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A102&lt;&gt;B102,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>201</v>
@@ -4854,16 +4864,16 @@
         <v>4</v>
       </c>
       <c r="I103" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A103&lt;&gt;B103,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>201</v>
@@ -4884,16 +4894,16 @@
         <v>4</v>
       </c>
       <c r="I104" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A104&lt;&gt;B104,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>201</v>
@@ -4914,16 +4924,16 @@
         <v>4</v>
       </c>
       <c r="I105" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A105&lt;&gt;B105,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>201</v>
@@ -4944,16 +4954,16 @@
         <v>4</v>
       </c>
       <c r="I106" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A106&lt;&gt;B106,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>201</v>
@@ -4974,16 +4984,16 @@
         <v>4</v>
       </c>
       <c r="I107" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A107&lt;&gt;B107,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>201</v>
@@ -5004,16 +5014,16 @@
         <v>4</v>
       </c>
       <c r="I108" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A108&lt;&gt;B108,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>201</v>
@@ -5034,16 +5044,16 @@
         <v>4</v>
       </c>
       <c r="I109" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A109&lt;&gt;B109,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>201</v>
@@ -5064,16 +5074,16 @@
         <v>4</v>
       </c>
       <c r="I110" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A110&lt;&gt;B110,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>201</v>
@@ -5094,16 +5104,16 @@
         <v>4</v>
       </c>
       <c r="I111" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A111&lt;&gt;B111,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>201</v>
@@ -5124,25 +5134,25 @@
         <v>4</v>
       </c>
       <c r="I112" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A112&lt;&gt;B112,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>189</v>
@@ -5154,25 +5164,25 @@
         <v>4</v>
       </c>
       <c r="I113" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A113&lt;&gt;B113,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>189</v>
@@ -5184,25 +5194,25 @@
         <v>4</v>
       </c>
       <c r="I114" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f>IF(A114&lt;&gt;B114,"FLAG","")</f>
+        <v>FLAG</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>189</v>
@@ -5214,25 +5224,25 @@
         <v>4</v>
       </c>
       <c r="I115" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A115&lt;&gt;B115,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>189</v>
@@ -5244,16 +5254,16 @@
         <v>4</v>
       </c>
       <c r="I116" t="str">
-        <f t="shared" si="3"/>
-        <v>FLAG</v>
+        <f>IF(A116&lt;&gt;B116,"FLAG","")</f>
+        <v/>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>201</v>
@@ -5274,16 +5284,16 @@
         <v>4</v>
       </c>
       <c r="I117" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A117&lt;&gt;B117,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>201</v>
@@ -5304,25 +5314,25 @@
         <v>4</v>
       </c>
       <c r="I118" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A118&lt;&gt;B118,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>189</v>
@@ -5334,25 +5344,25 @@
         <v>4</v>
       </c>
       <c r="I119" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A119&lt;&gt;B119,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>189</v>
@@ -5364,16 +5374,16 @@
         <v>4</v>
       </c>
       <c r="I120" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A120&lt;&gt;B120,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>201</v>
@@ -5394,25 +5404,25 @@
         <v>4</v>
       </c>
       <c r="I121" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A121&lt;&gt;B121,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>189</v>
@@ -5424,25 +5434,25 @@
         <v>4</v>
       </c>
       <c r="I122" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A122&lt;&gt;B122,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>189</v>
@@ -5454,25 +5464,25 @@
         <v>4</v>
       </c>
       <c r="I123" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A123&lt;&gt;B123,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>189</v>
@@ -5484,16 +5494,16 @@
         <v>4</v>
       </c>
       <c r="I124" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A124&lt;&gt;B124,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>201</v>
@@ -5514,25 +5524,25 @@
         <v>4</v>
       </c>
       <c r="I125" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A125&lt;&gt;B125,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>189</v>
@@ -5544,25 +5554,25 @@
         <v>4</v>
       </c>
       <c r="I126" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A126&lt;&gt;B126,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>164</v>
+        <v>247</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>189</v>
@@ -5573,26 +5583,22 @@
       <c r="H127" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I127" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>189</v>
@@ -5603,26 +5609,22 @@
       <c r="H128" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I128" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>245</v>
+        <v>162</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>245</v>
+        <v>162</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>201</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>189</v>
@@ -5636,19 +5638,19 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>161</v>
+        <v>252</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>161</v>
+        <v>252</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>189</v>
@@ -5660,68 +5662,16 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H131" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H132" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I131">
-    <sortCondition ref="C3:C131"/>
-    <sortCondition ref="G3:G131"/>
-    <sortCondition ref="H3:H131"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I129">
+    <sortCondition ref="C3:C129"/>
+    <sortCondition ref="G3:G129"/>
+    <sortCondition ref="H3:H129"/>
   </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="I116:I117">
-    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I116)))</formula>
+  <conditionalFormatting sqref="I114:I115">
+    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I114)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
       <colorScale>
@@ -5734,8 +5684,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I32:I115 I3:I4 I7:I30">
-    <cfRule type="containsText" dxfId="7" priority="43" operator="containsText" text="FLAG">
+  <conditionalFormatting sqref="I32:I113 I3:I4 I7:I30">
+    <cfRule type="containsText" dxfId="8" priority="43" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I3)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="44">
@@ -5750,7 +5700,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I5)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -5765,7 +5715,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I6)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -5780,7 +5730,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I31)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -5795,7 +5745,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -5815,7 +5765,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC7E8D0-101B-584C-9021-A7CDF92F27AF}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -6559,10 +6509,85 @@
         <v/>
       </c>
     </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" t="str">
+        <f>IF(A26&lt;&gt;B26,"FLAG","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" t="str">
+        <f>IF(A27&lt;&gt;B27,"FLAG","")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I22">
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -6575,9 +6600,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
+  <conditionalFormatting sqref="I24:I25">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I24)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -6590,9 +6615,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24:I25">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I24)))</formula>
+  <conditionalFormatting sqref="I26:I27">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I26)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>

--- a/tabular/sublineage/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/sublineage/herv_sublineage_ltr_data_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C708C70E-DD6C-F54B-91D1-ECF75CC54BC4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA84785D-E1C4-2F4D-9740-73FDCE855107}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="720" windowWidth="21060" windowHeight="16940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="720" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ltr_lineage_table" sheetId="1" r:id="rId1"/>
@@ -2132,7 +2132,7 @@
         <v>4</v>
       </c>
       <c r="I11" t="str">
-        <f>IF(A11&lt;&gt;B11,"FLAG","")</f>
+        <f t="shared" ref="I11:I42" si="0">IF(A11&lt;&gt;B11,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="str">
-        <f>IF(A12&lt;&gt;B12,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="str">
-        <f>IF(A13&lt;&gt;B13,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="str">
-        <f>IF(A14&lt;&gt;B14,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
         <v>4</v>
       </c>
       <c r="I15" t="str">
-        <f>IF(A15&lt;&gt;B15,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="str">
-        <f>IF(A16&lt;&gt;B16,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>4</v>
       </c>
       <c r="I17" t="str">
-        <f>IF(A17&lt;&gt;B17,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
         <v>4</v>
       </c>
       <c r="I18" t="str">
-        <f>IF(A18&lt;&gt;B18,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
         <v>4</v>
       </c>
       <c r="I19" t="str">
-        <f>IF(A19&lt;&gt;B19,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="str">
-        <f>IF(A20&lt;&gt;B20,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
         <v>4</v>
       </c>
       <c r="I21" t="str">
-        <f>IF(A21&lt;&gt;B21,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
         <v>4</v>
       </c>
       <c r="I22" t="str">
-        <f>IF(A22&lt;&gt;B22,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="I23" t="str">
-        <f>IF(A23&lt;&gt;B23,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="str">
-        <f>IF(A24&lt;&gt;B24,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
         <v>4</v>
       </c>
       <c r="I25" t="str">
-        <f>IF(A25&lt;&gt;B25,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
         <v>4</v>
       </c>
       <c r="I26" t="str">
-        <f>IF(A26&lt;&gt;B26,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
         <v>4</v>
       </c>
       <c r="I27" t="str">
-        <f>IF(A27&lt;&gt;B27,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>4</v>
       </c>
       <c r="I28" t="str">
-        <f>IF(A28&lt;&gt;B28,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
         <v>4</v>
       </c>
       <c r="I29" t="str">
-        <f>IF(A29&lt;&gt;B29,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
         <v>4</v>
       </c>
       <c r="I30" t="str">
-        <f>IF(A30&lt;&gt;B30,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
         <v>4</v>
       </c>
       <c r="I31" t="str">
-        <f>IF(A31&lt;&gt;B31,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
         <v>4</v>
       </c>
       <c r="I32" t="str">
-        <f>IF(A32&lt;&gt;B32,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
         <v>4</v>
       </c>
       <c r="I33" t="str">
-        <f>IF(A33&lt;&gt;B33,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
         <v>4</v>
       </c>
       <c r="I34" t="str">
-        <f>IF(A34&lt;&gt;B34,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
         <v>4</v>
       </c>
       <c r="I35" t="str">
-        <f>IF(A35&lt;&gt;B35,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
         <v>4</v>
       </c>
       <c r="I36" t="str">
-        <f>IF(A36&lt;&gt;B36,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
         <v>4</v>
       </c>
       <c r="I37" t="str">
-        <f>IF(A37&lt;&gt;B37,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
         <v>4</v>
       </c>
       <c r="I38" t="str">
-        <f>IF(A38&lt;&gt;B38,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
         <v>4</v>
       </c>
       <c r="I39" t="str">
-        <f>IF(A39&lt;&gt;B39,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
         <v>56</v>
       </c>
       <c r="I40" t="str">
-        <f>IF(A40&lt;&gt;B40,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v>FLAG</v>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
         <v>56</v>
       </c>
       <c r="I41" t="str">
-        <f>IF(A41&lt;&gt;B41,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v>FLAG</v>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
         <v>56</v>
       </c>
       <c r="I42" t="str">
-        <f>IF(A42&lt;&gt;B42,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
         <v>56</v>
       </c>
       <c r="I43" t="str">
-        <f>IF(A43&lt;&gt;B43,"FLAG","")</f>
+        <f t="shared" ref="I43:I74" si="1">IF(A43&lt;&gt;B43,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
         <v>56</v>
       </c>
       <c r="I44" t="str">
-        <f>IF(A44&lt;&gt;B44,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
         <v>56</v>
       </c>
       <c r="I45" t="str">
-        <f>IF(A45&lt;&gt;B45,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
         <v>4</v>
       </c>
       <c r="I46" t="str">
-        <f>IF(A46&lt;&gt;B46,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
         <v>4</v>
       </c>
       <c r="I47" t="str">
-        <f>IF(A47&lt;&gt;B47,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
         <v>4</v>
       </c>
       <c r="I48" t="str">
-        <f>IF(A48&lt;&gt;B48,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
         <v>4</v>
       </c>
       <c r="I49" t="str">
-        <f>IF(A49&lt;&gt;B49,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
         <v>4</v>
       </c>
       <c r="I50" t="str">
-        <f>IF(A50&lt;&gt;B50,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
         <v>4</v>
       </c>
       <c r="I51" t="str">
-        <f>IF(A51&lt;&gt;B51,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
         <v>4</v>
       </c>
       <c r="I52" t="str">
-        <f>IF(A52&lt;&gt;B52,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
         <v>4</v>
       </c>
       <c r="I53" t="str">
-        <f>IF(A53&lt;&gt;B53,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
         <v>4</v>
       </c>
       <c r="I54" t="str">
-        <f>IF(A54&lt;&gt;B54,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
         <v>4</v>
       </c>
       <c r="I55" t="str">
-        <f>IF(A55&lt;&gt;B55,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>4</v>
       </c>
       <c r="I56" t="str">
-        <f>IF(A56&lt;&gt;B56,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
         <v>4</v>
       </c>
       <c r="I57" t="str">
-        <f>IF(A57&lt;&gt;B57,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         <v>4</v>
       </c>
       <c r="I58" t="str">
-        <f>IF(A58&lt;&gt;B58,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
         <v>4</v>
       </c>
       <c r="I59" t="str">
-        <f>IF(A59&lt;&gt;B59,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
         <v>4</v>
       </c>
       <c r="I60" t="str">
-        <f>IF(A60&lt;&gt;B60,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
         <v>4</v>
       </c>
       <c r="I61" t="str">
-        <f>IF(A61&lt;&gt;B61,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
         <v>4</v>
       </c>
       <c r="I62" t="str">
-        <f>IF(A62&lt;&gt;B62,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3692,7 +3692,7 @@
         <v>4</v>
       </c>
       <c r="I63" t="str">
-        <f>IF(A63&lt;&gt;B63,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
         <v>4</v>
       </c>
       <c r="I64" t="str">
-        <f>IF(A64&lt;&gt;B64,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
         <v>4</v>
       </c>
       <c r="I65" t="str">
-        <f>IF(A65&lt;&gt;B65,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
         <v>4</v>
       </c>
       <c r="I66" t="str">
-        <f>IF(A66&lt;&gt;B66,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
         <v>4</v>
       </c>
       <c r="I67" t="str">
-        <f>IF(A67&lt;&gt;B67,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
         <v>4</v>
       </c>
       <c r="I68" t="str">
-        <f>IF(A68&lt;&gt;B68,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
         <v>4</v>
       </c>
       <c r="I69" t="str">
-        <f>IF(A69&lt;&gt;B69,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
         <v>4</v>
       </c>
       <c r="I70" t="str">
-        <f>IF(A70&lt;&gt;B70,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
         <v>4</v>
       </c>
       <c r="I71" t="str">
-        <f>IF(A71&lt;&gt;B71,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
         <v>4</v>
       </c>
       <c r="I72" t="str">
-        <f>IF(A72&lt;&gt;B72,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
         <v>4</v>
       </c>
       <c r="I73" t="str">
-        <f>IF(A73&lt;&gt;B73,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
         <v>4</v>
       </c>
       <c r="I74" t="str">
-        <f>IF(A74&lt;&gt;B74,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
         <v>4</v>
       </c>
       <c r="I75" t="str">
-        <f>IF(A75&lt;&gt;B75,"FLAG","")</f>
+        <f t="shared" ref="I75:I91" si="2">IF(A75&lt;&gt;B75,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
         <v>4</v>
       </c>
       <c r="I76" t="str">
-        <f>IF(A76&lt;&gt;B76,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
         <v>4</v>
       </c>
       <c r="I77" t="str">
-        <f>IF(A77&lt;&gt;B77,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
         <v>4</v>
       </c>
       <c r="I78" t="str">
-        <f>IF(A78&lt;&gt;B78,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
         <v>4</v>
       </c>
       <c r="I79" t="str">
-        <f>IF(A79&lt;&gt;B79,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
         <v>4</v>
       </c>
       <c r="I80" t="str">
-        <f>IF(A80&lt;&gt;B80,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
         <v>4</v>
       </c>
       <c r="I81" t="str">
-        <f>IF(A81&lt;&gt;B81,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
         <v>4</v>
       </c>
       <c r="I82" t="str">
-        <f>IF(A82&lt;&gt;B82,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
         <v>4</v>
       </c>
       <c r="I83" t="str">
-        <f>IF(A83&lt;&gt;B83,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>4</v>
       </c>
       <c r="I84" t="str">
-        <f>IF(A84&lt;&gt;B84,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
         <v>4</v>
       </c>
       <c r="I85" t="str">
-        <f>IF(A85&lt;&gt;B85,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
         <v>4</v>
       </c>
       <c r="I86" t="str">
-        <f>IF(A86&lt;&gt;B86,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
         <v>4</v>
       </c>
       <c r="I87" t="str">
-        <f>IF(A87&lt;&gt;B87,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
         <v>4</v>
       </c>
       <c r="I88" t="str">
-        <f>IF(A88&lt;&gt;B88,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
         <v>4</v>
       </c>
       <c r="I89" t="str">
-        <f>IF(A89&lt;&gt;B89,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
         <v>4</v>
       </c>
       <c r="I90" t="str">
-        <f>IF(A90&lt;&gt;B90,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
         <v>4</v>
       </c>
       <c r="I91" t="str">
-        <f>IF(A91&lt;&gt;B91,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
         <v>4</v>
       </c>
       <c r="I99" t="str">
-        <f>IF(A99&lt;&gt;B99,"FLAG","")</f>
+        <f t="shared" ref="I99:I126" si="3">IF(A99&lt;&gt;B99,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
         <v>4</v>
       </c>
       <c r="I100" t="str">
-        <f>IF(A100&lt;&gt;B100,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
         <v>4</v>
       </c>
       <c r="I101" t="str">
-        <f>IF(A101&lt;&gt;B101,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>4</v>
       </c>
       <c r="I102" t="str">
-        <f>IF(A102&lt;&gt;B102,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
         <v>4</v>
       </c>
       <c r="I103" t="str">
-        <f>IF(A103&lt;&gt;B103,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
         <v>4</v>
       </c>
       <c r="I104" t="str">
-        <f>IF(A104&lt;&gt;B104,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>4</v>
       </c>
       <c r="I105" t="str">
-        <f>IF(A105&lt;&gt;B105,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
         <v>4</v>
       </c>
       <c r="I106" t="str">
-        <f>IF(A106&lt;&gt;B106,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
         <v>4</v>
       </c>
       <c r="I107" t="str">
-        <f>IF(A107&lt;&gt;B107,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
         <v>4</v>
       </c>
       <c r="I108" t="str">
-        <f>IF(A108&lt;&gt;B108,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
         <v>4</v>
       </c>
       <c r="I109" t="str">
-        <f>IF(A109&lt;&gt;B109,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
         <v>4</v>
       </c>
       <c r="I110" t="str">
-        <f>IF(A110&lt;&gt;B110,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
         <v>4</v>
       </c>
       <c r="I111" t="str">
-        <f>IF(A111&lt;&gt;B111,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
         <v>4</v>
       </c>
       <c r="I112" t="str">
-        <f>IF(A112&lt;&gt;B112,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
         <v>4</v>
       </c>
       <c r="I113" t="str">
-        <f>IF(A113&lt;&gt;B113,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
         <v>4</v>
       </c>
       <c r="I114" t="str">
-        <f>IF(A114&lt;&gt;B114,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v>FLAG</v>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
         <v>4</v>
       </c>
       <c r="I115" t="str">
-        <f>IF(A115&lt;&gt;B115,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
         <v>4</v>
       </c>
       <c r="I116" t="str">
-        <f>IF(A116&lt;&gt;B116,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
         <v>4</v>
       </c>
       <c r="I117" t="str">
-        <f>IF(A117&lt;&gt;B117,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
         <v>4</v>
       </c>
       <c r="I118" t="str">
-        <f>IF(A118&lt;&gt;B118,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
         <v>4</v>
       </c>
       <c r="I119" t="str">
-        <f>IF(A119&lt;&gt;B119,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
         <v>4</v>
       </c>
       <c r="I120" t="str">
-        <f>IF(A120&lt;&gt;B120,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5404,7 +5404,7 @@
         <v>4</v>
       </c>
       <c r="I121" t="str">
-        <f>IF(A121&lt;&gt;B121,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
         <v>4</v>
       </c>
       <c r="I122" t="str">
-        <f>IF(A122&lt;&gt;B122,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
         <v>4</v>
       </c>
       <c r="I123" t="str">
-        <f>IF(A123&lt;&gt;B123,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
         <v>4</v>
       </c>
       <c r="I124" t="str">
-        <f>IF(A124&lt;&gt;B124,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
         <v>4</v>
       </c>
       <c r="I125" t="str">
-        <f>IF(A125&lt;&gt;B125,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
         <v>4</v>
       </c>
       <c r="I126" t="str">
-        <f>IF(A126&lt;&gt;B126,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>

--- a/tabular/sublineage/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/sublineage/herv_sublineage_ltr_data_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA84785D-E1C4-2F4D-9740-73FDCE855107}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7141BC-2131-5342-9C07-E83C8F019836}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7200" yWindow="720" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
